--- a/docs/cadrage/equipe-09-release-planning-v1.0.xlsx
+++ b/docs/cadrage/equipe-09-release-planning-v1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabbe\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1847A225-0169-454E-A00A-991FA645D8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF56F8E-6FF1-41C5-A350-D7C0BAB57B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Garde" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,33 @@
     <sheet name="Release Planning" sheetId="3" r:id="rId3"/>
     <sheet name="Burnup global" sheetId="4" r:id="rId4"/>
     <sheet name="Auto-évaluation" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="157">
   <si>
     <t>A</t>
   </si>
@@ -56,21 +76,39 @@
     <t>Équipe n°</t>
   </si>
   <si>
+    <t xml:space="preserve">Groupe  9 </t>
+  </si>
+  <si>
     <t>Membres</t>
   </si>
   <si>
+    <t>Amine MAHI, Axel FORTUNATO, Médy SIMON, Ryma DINARI,Bassim Tabbeb</t>
+  </si>
+  <si>
     <t>Sprint concerné</t>
   </si>
   <si>
+    <t>Cadrage</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
+    <t xml:space="preserve">V1.0 </t>
+  </si>
+  <si>
     <t>Date de remise</t>
   </si>
   <si>
+    <t>29/06/2026 13h00</t>
+  </si>
+  <si>
     <t>Statut</t>
   </si>
   <si>
+    <t>Draft</t>
+  </si>
+  <si>
     <t>💡 Convention de nommage du fichier :</t>
   </si>
   <si>
@@ -98,7 +136,7 @@
     <t>✅ BON</t>
   </si>
   <si>
-    <t>« Sprint 1 : Objectif = setup MVP F1 + F2 · Capacité 28 h-pers · Vélocité 10 SP · Stories US-01, US-02 »</t>
+    <t>« Sprint 1 : Objectif = setup MVP F1 + F2 · Capacité 20 h-pers · Vélocité 10 SP · Stories US-01, US-02 »</t>
   </si>
   <si>
     <t>❌ À ÉVITER</t>
@@ -131,9 +169,6 @@
     <t>Release / Jalon</t>
   </si>
   <si>
-    <t>Cadrage</t>
-  </si>
-  <si>
     <t>Lundi matin</t>
   </si>
   <si>
@@ -146,6 +181,9 @@
     <t>Produire les 7 artefacts agiles (Vision, Personas, Customer Journey, Story Map, Release Planning, Product Backlog, Sprint Backlog)</t>
   </si>
   <si>
+    <t>cadrage</t>
+  </si>
+  <si>
     <t>📋 Validation PO 14h00</t>
   </si>
   <si>
@@ -158,9 +196,6 @@
     <t>14h00 – 18h00</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>Setup technique + démarrage MVP (F1 inscription, F2 upload cours)</t>
   </si>
   <si>
@@ -179,51 +214,73 @@
     <t>9h00 – 12h30</t>
   </si>
   <si>
+    <t>Génération quiz F3 (Llama 3.1 8B via Ollama), perturbation J2 (latence)</t>
+  </si>
+  <si>
+    <t>US-03, US-04</t>
+  </si>
+  <si>
+    <t>⚡ Perturbation J2 à 10h</t>
+  </si>
+  <si>
+    <t>Sprint 3</t>
+  </si>
+  <si>
+    <t>Mardi PM</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Correction + scoring F4/F5 + intégration ADR-J2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Calibri"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">US-05, US-06, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1B4B"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>US-07</t>
+    </r>
+  </si>
+  <si>
+    <t>Sprint 4</t>
+  </si>
+  <si>
+    <t>Mercredi matin</t>
+  </si>
+  <si>
+    <t>5-8</t>
+  </si>
+  <si>
+    <t>Historique F6 + sécurisation prompt injection (perturbation J3)</t>
+  </si>
+  <si>
+    <t>US-08 + patch sécurité</t>
+  </si>
+  <si>
+    <t>⚡ Perturbation J3 à 10h</t>
+  </si>
+  <si>
+    <t>Sprint 5</t>
+  </si>
+  <si>
+    <t>Mercredi PM</t>
+  </si>
+  <si>
     <t>8-10</t>
   </si>
   <si>
-    <t>Génération quiz F3 (Llama 3.1 8B via Ollama), perturbation J2 (latence)</t>
-  </si>
-  <si>
-    <t>US-03</t>
-  </si>
-  <si>
-    <t>⚡ Perturbation J2 à 10h</t>
-  </si>
-  <si>
-    <t>Sprint 3</t>
-  </si>
-  <si>
-    <t>Mardi PM</t>
-  </si>
-  <si>
-    <t>Correction + scoring F4/F5 + intégration ADR-J2</t>
-  </si>
-  <si>
-    <t>US-04, US-05</t>
-  </si>
-  <si>
-    <t>Sprint 4</t>
-  </si>
-  <si>
-    <t>Mercredi matin</t>
-  </si>
-  <si>
-    <t>Historique F6 + sécurisation prompt injection (perturbation J3)</t>
-  </si>
-  <si>
-    <t>US-06 + patch sécurité</t>
-  </si>
-  <si>
-    <t>⚡ Perturbation J3 à 10h</t>
-  </si>
-  <si>
-    <t>Sprint 5</t>
-  </si>
-  <si>
-    <t>Mercredi PM</t>
-  </si>
-  <si>
     <t>Conformité RGPD SAR (J3-bis) + finalisation MVP F1-F6</t>
   </si>
   <si>
@@ -245,7 +302,7 @@
     <t>Stories Release 2 (2-3 pistes choisies), crise utilisateur J4</t>
   </si>
   <si>
-    <t>[US-XX selon Release 2 retenue]</t>
+    <t>US-09, US-10</t>
   </si>
   <si>
     <t>⚡ Perturbation J4 à 10h</t>
@@ -260,13 +317,10 @@
     <t>14h00 – 17h00</t>
   </si>
   <si>
-    <t>6-8</t>
-  </si>
-  <si>
     <t>Finalisation Release 2 + post-mortem J4 + démo prête</t>
   </si>
   <si>
-    <t>[US-XX Release 2] + post-mortem</t>
+    <t>US-21, US-22 + post-mortem</t>
   </si>
   <si>
     <t>🚀 Release 2 17h</t>
@@ -293,9 +347,6 @@
     <t>~ 50-60 SP</t>
   </si>
   <si>
-    <t>Capacité totale = 203.0 h-pers (équipe de 7 personnes)</t>
-  </si>
-  <si>
     <t>📌 LÉGENDE</t>
   </si>
   <si>
@@ -365,9 +416,6 @@
     <t>Lun 13h30</t>
   </si>
   <si>
-    <t>[à compléter]</t>
-  </si>
-  <si>
     <t>56 (scope initial)</t>
   </si>
   <si>
@@ -425,7 +473,7 @@
     <t>Les 7 sprints sont planifiés avec jour, horaires et capacité (h-pers) chiffrée</t>
   </si>
   <si>
-    <t>L'équipe taille est explicite (ex. 7 personnes), pas de capacité "floue"</t>
+    <t>✅ Oui   ☐ Partiel   ☐ Non</t>
   </si>
   <si>
     <t>Chaque sprint a un objectif clair, mesurable, livrable en démo</t>
@@ -434,6 +482,9 @@
     <t>Chaque sprint liste au moins 1 user story engagée (tag US-XX du Product Backlog)</t>
   </si>
   <si>
+    <t xml:space="preserve"> ✅Oui  ☐  Partiel   ☐ Non</t>
+  </si>
+  <si>
     <t>La Release 1 (MVP) est explicitement positionnée à la fin du Sprint 5 (mercredi 17h45)</t>
   </si>
   <si>
@@ -449,25 +500,37 @@
     <t>Le Release Planning a été co-construit en équipe (toutes les voix entendues)</t>
   </si>
   <si>
-    <t xml:space="preserve">Groupe  9 </t>
-  </si>
-  <si>
-    <t>Amine MAHI, Axel FORTUNATO, Médy SIMON, Ryma DINARI,Bassim Tabbeb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V1.0 </t>
-  </si>
-  <si>
-    <t>29/06/2026 13h00</t>
-  </si>
-  <si>
-    <t>Draft</t>
-  </si>
-  <si>
-    <t>✅ Oui   ☐ Partiel   ☐ Non</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ☐  Oui  ✅ Partiel   ☐ Non</t>
+    <t>Capacité totale = 145 h-pers (équipe de 5 personnes)</t>
+  </si>
+  <si>
+    <t>L'équipe taille est explicite (ex. 5 personnes), pas de capacité "floue"</t>
+  </si>
+  <si>
+    <t>Jour, horaires et capacité h-pers chiffrés pour chaque sprint, du Cadrage à la Soutenance.</t>
+  </si>
+  <si>
+    <t>Équipe de 5 personnes, capacités recalculées en conséquence (3.5h × 5 = 17.5h ; 4h × 5 = 20h par sprint)</t>
+  </si>
+  <si>
+    <t>Chaque sprint a un objectif fonctionnel daté et démontrable (ex. Sprint 1 = F1+F2, Sprint 3 = F4/F5).</t>
+  </si>
+  <si>
+    <t>Tags US-01 à US-10 repris du Product Backlog pour les sprints 1 à 6 ; US-21/US-22 pour le Sprint 7 (numérotation Release 2 du backlog), à reconfirmer une fois le Product Backlog totalement figé.</t>
+  </si>
+  <si>
+    <t>Release 1 (MVP) positionnée mercredi 17h45, jalon explicite sur la ligne Sprint 5.</t>
+  </si>
+  <si>
+    <t>Release 2 positionnée jeudi 17h, jalon explicite sur la ligne Sprint 7.</t>
+  </si>
+  <si>
+    <t>Perturbations J2 (latence), J3 (sécurité), J3-bis (RGPD) et J4 (crise utilisateur) positionnées aux créneaux imposés par le calendrier officiel.</t>
+  </si>
+  <si>
+    <t>Scope initial fixé à 56 SP. Colonne réel actuellement projetée à l'identique de l'idéal ; sera mise à jour avec les vrais SP livrés après chaque Sprint Review</t>
+  </si>
+  <si>
+    <t>Capacité et vélocité ajustées ensemble en visio le 29/06 matin (équipe de 5), choix discutés collectivement avant validation.</t>
   </si>
 </sst>
 </file>
@@ -480,112 +543,144 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="72"/>
       <color rgb="FF1E1B4B"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF1E1B4B"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFF59E0B"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="24"/>
       <color rgb="FF1E1B4B"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <i/>
       <sz val="12"/>
       <color rgb="FF475569"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF475569"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF475569"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFF59E0B"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF475569"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1E1B4B"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF475569"/>
       <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF475569"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFF59E0B"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FF1E1B4B"/>
       <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF475569"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF16A34A"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFDC2626"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF1E1B4B"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF1E1B4B"/>
       <name val="Calibri"/>
     </font>
@@ -593,49 +688,41 @@
       <sz val="10"/>
       <color rgb="FFB45309"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFDC2626"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF16A34A"/>
       <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF1E1B4B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF1E1B4B"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF475569"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF1E1B4B"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF1E1B4B"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF475569"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="10">
@@ -648,49 +735,49 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8FAFC"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E1B4B"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2FF"/>
         <bgColor rgb="FFF8FAFC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E1B4B"/>
-        <bgColor rgb="FF1E1B4B"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF8FAFC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF2FF"/>
+        <fgColor rgb="FFFFFBEB"/>
+        <bgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3C7"/>
+        <bgColor rgb="FFFFFBEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCFCE7"/>
         <bgColor rgb="FFEEF2FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFBEB"/>
-        <bgColor rgb="FFFFFBEB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
-        <bgColor rgb="FFFEF3C7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCFCE7"/>
-        <bgColor rgb="FFDCFCE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE0E7FF"/>
-        <bgColor rgb="FFE0E7FF"/>
+        <bgColor rgb="FFEEF2FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -736,7 +823,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -749,69 +836,75 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -820,18 +913,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFDC2626"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFCCCCCC"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFEF3C7"/>
+      <rgbColor rgb="FFDCFCE7"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFE0E7FF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFEEF2FF"/>
+      <rgbColor rgb="FFF8FAFC"/>
+      <rgbColor rgb="FFFFFBEB"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFF59E0B"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF475569"/>
+      <rgbColor rgb="FF94A3B8"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF16A34A"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FFB45309"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF1E1B4B"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -848,10 +1006,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -889,234 +1047,128 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1129,7 +1181,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:B21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
@@ -1145,7 +1197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>2</v>
       </c>
@@ -1160,25 +1212,26 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -1190,78 +1243,79 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B12" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1272,371 +1326,372 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A1" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="46" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="21">
+        <v>17.5</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="24">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="19">
-        <v>24.5</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="21" t="s">
+      <c r="E11" s="24">
+        <v>8</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="27">
+        <v>17.5</v>
+      </c>
+      <c r="E12" s="27">
+        <v>11</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12" s="26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="24">
+        <v>20</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="27">
+        <v>17.5</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="30">
+        <v>20</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="27">
+        <v>17.5</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="26" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="30">
+        <v>15</v>
+      </c>
+      <c r="E17" s="30">
+        <v>10</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="22">
-        <v>28</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="21" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="25">
-        <v>24.5</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="21" t="s">
+      <c r="E18" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="22">
-        <v>28</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="H13" s="21" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="25">
-        <v>24.5</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="27" t="s">
+      <c r="F18" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="28">
-        <v>28</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="H15" s="27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="25">
-        <v>24.5</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="G16" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" s="28">
-        <v>21</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="H17" s="27" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="30" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="G18" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="H18" s="30" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="32">
-        <v>203</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="F19" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H18" s="32" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="34">
+        <v>145</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+    </row>
+    <row r="21" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="35" t="s">
-        <v>91</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="37" t="s">
+        <v>96</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="36" t="s">
-        <v>93</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="38" t="s">
+        <v>98</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="37" t="s">
-        <v>95</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="39" t="s">
+        <v>100</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="38" t="s">
-        <v>97</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="40" t="s">
+        <v>102</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1645,320 +1700,537 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A1" s="45" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>108</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="B9" s="40" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C8" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="43">
         <v>0</v>
       </c>
-      <c r="D9" s="44" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" s="40" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" s="40">
+      <c r="D9" s="44">
+        <v>0</v>
+      </c>
+      <c r="E9" s="43" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="43">
         <v>8</v>
       </c>
-      <c r="D10" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="40" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="39" t="s">
+      <c r="D10" s="43">
+        <v>8</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="43">
+        <v>16</v>
+      </c>
+      <c r="D11" s="43">
+        <v>16</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="43">
+        <v>24</v>
+      </c>
+      <c r="D12" s="43">
+        <v>24</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="43">
+        <v>32</v>
+      </c>
+      <c r="D13" s="43">
+        <v>32</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="43">
+        <v>40</v>
+      </c>
+      <c r="D14" s="43">
+        <v>40</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="43">
         <v>48</v>
       </c>
-      <c r="B11" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="40">
-        <v>16</v>
-      </c>
-      <c r="D11" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" s="40" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="40">
-        <v>24</v>
-      </c>
-      <c r="D12" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="E12" s="40" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="C13" s="40">
-        <v>32</v>
-      </c>
-      <c r="D13" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="C14" s="40">
-        <v>40</v>
-      </c>
-      <c r="D14" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" s="40" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="40">
+      <c r="D15" s="43">
         <v>48</v>
       </c>
-      <c r="D15" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="40" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="B16" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="C16" s="40">
+      <c r="E15" s="43" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" s="43">
         <v>56</v>
       </c>
-      <c r="D16" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="E16" s="40" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D16" s="43">
+        <v>56</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A2:D14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="4" max="4" width="149.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>130</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>134</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="41" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" s="41"/>
+      <c r="B6" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="41" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" s="41"/>
+      <c r="B7" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="D8" s="41"/>
+      <c r="B8" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="41" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>147</v>
-      </c>
-      <c r="D9" s="41"/>
+      <c r="B9" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="D10" s="41"/>
+      <c r="B10" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="C11" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="C11" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="D11" s="41"/>
+      <c r="D11" s="46" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="D12" s="41"/>
+      <c r="B12" s="45" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>147</v>
-      </c>
-      <c r="D13" s="41"/>
+      <c r="B13" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" s="47" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="41" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14" s="42" t="s">
-        <v>147</v>
-      </c>
-      <c r="D14" s="41"/>
+      <c r="B14" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>156</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1AF8B11-5500-43A3-A9E8-82B46EC36721}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010047E35FF551331140B273BB19EEA78143" ma:contentTypeVersion="3" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="530aa9c009d146a80c49f02630cdfc2d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aa7a771e-02cb-4c1a-a357-20624cfae5a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d97f7f33240c9425ea547835b506498e" ns2:_="">
+    <xsd:import namespace="aa7a771e-02cb-4c1a-a357-20624cfae5a5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="aa7a771e-02cb-4c1a-a357-20624cfae5a5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Type de contenu"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titre"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91B4EAAE-D21E-4A80-B458-ED6CCF2F6844}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA6D77C1-AD14-4ED5-A543-1E9506703594}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="aa7a771e-02cb-4c1a-a357-20624cfae5a5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F28AFF3-9EEE-4EE8-9F12-CD0B71F673E2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>